--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,801 +453,673 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2998263040386018</v>
+        <v>0.377137726415987</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6786330087422461</v>
+        <v>0.6819230203249801</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3788067047036443</v>
+        <v>-0.3047852939089931</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03821161685388849</v>
+        <v>0.5067129829003074</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9881997410505858</v>
+        <v>0.6236056588043462</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9499881241966973</v>
+        <v>-0.1168926759040387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6981967658399986</v>
+        <v>0.4826879696520813</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9618675435715549</v>
+        <v>0.6381519303469889</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2636707777315563</v>
+        <v>-0.1554639606949076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6653887546921069</v>
+        <v>0.5821360344750989</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8928525733979231</v>
+        <v>0.3890671215833203</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2274638187058162</v>
+        <v>0.1930689128917786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7008873783771058</v>
+        <v>0.5939028475711893</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2092360458394001</v>
+        <v>0.3708415712880428</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4916513325377057</v>
+        <v>0.2230612762831464</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7946522605350057</v>
+        <v>0.4526094186033047</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2131930936207022</v>
+        <v>0.6554864030257319</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5814591669143035</v>
+        <v>-0.2028769844224272</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1934114535670716</v>
+        <v>0.007144722440186396</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7284487945050352</v>
+        <v>0.00200729846300878</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5350373409379636</v>
+        <v>0.005137423977177617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7104593498919569</v>
+        <v>0.4210779910000516</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2046486373559072</v>
+        <v>0.5318215606254093</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5058107125360497</v>
+        <v>-0.1107435696253578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2039166220200799</v>
+        <v>0.6217739390885568</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7244404833409179</v>
+        <v>0.7178644499294237</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5205238613208381</v>
+        <v>-0.09609051084086684</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7751790806554131</v>
+        <v>0.4999689484462459</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2325269260997694</v>
+        <v>0.6304834817185002</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5426521545556436</v>
+        <v>-0.1305145332722543</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.786522272582814</v>
+        <v>0.3748139492863968</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2181042064093937</v>
+        <v>0.6591115689430123</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5684180661734204</v>
+        <v>-0.2842976196566154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04932895908953001</v>
+        <v>0.5054689840253346</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04869835185986944</v>
+        <v>0.517645920346168</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0006306072296605736</v>
+        <v>-0.01217693632083339</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4679456271284002</v>
+        <v>0.6350377587486356</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6285957059289867</v>
+        <v>0.5722440249060337</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1606500788005866</v>
+        <v>0.0627937338426019</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.696538127755517</v>
+        <v>0.4866146808238492</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9593457271895101</v>
+        <v>0.628376371919688</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.262807599433993</v>
+        <v>-0.1417616910958387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7452922235243273</v>
+        <v>0.7018791914916932</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2190170106289026</v>
+        <v>0.6514921141876674</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5262752128954248</v>
+        <v>0.05038707730402581</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3031764128924245</v>
+        <v>0.5121194266111841</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6805874722831118</v>
+        <v>0.4672752066773882</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3774110593906873</v>
+        <v>0.04484421993379595</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6394434457828111</v>
+        <v>0.5114603801548535</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3042848258936163</v>
+        <v>0.4950245861112515</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3351586198891948</v>
+        <v>0.01643579404360201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8808088475108313</v>
+        <v>0.5117438699026333</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6709391648735027</v>
+        <v>0.5783520655087575</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2098696826373286</v>
+        <v>-0.06660819560612419</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2026758162088315</v>
+        <v>0.3944422820523952</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7262346095896625</v>
+        <v>0.6323206089811551</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.523558793380831</v>
+        <v>-0.2378783269287599</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3825267256069306</v>
+        <v>0.6241900753099733</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5914851814234305</v>
+        <v>0.7123033824506657</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2089584558165</v>
+        <v>-0.08811330714069243</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7812368946973154</v>
+        <v>0.3953240055330086</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2322245889484033</v>
+        <v>0.6374874687148173</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5490123057489121</v>
+        <v>-0.2421634631818088</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9843394352211795</v>
+        <v>0.3696126804517221</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7177972369629838</v>
+        <v>0.6587925800627129</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2665421982581957</v>
+        <v>-0.2891798996109908</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7077874569400721</v>
+        <v>0.5298472494069106</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9848326078896597</v>
+        <v>0.5849256027020964</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2770451509495876</v>
+        <v>-0.05507835329518573</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9803288417127399</v>
+        <v>0.6271924553240629</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7117133034726968</v>
+        <v>0.7143641137674952</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2686155382400431</v>
+        <v>-0.08717165844343233</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.704976658545964</v>
+        <v>0.6269192653790212</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9830410037086652</v>
+        <v>0.7130312295005876</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2780643451627012</v>
+        <v>-0.08611196412156641</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7083213156189234</v>
+        <v>0.6976248884636664</v>
       </c>
       <c r="C27" t="n">
-        <v>0.984458286137591</v>
+        <v>0.6485031086644256</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2761369705186676</v>
+        <v>0.04912177979924082</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7034229024776182</v>
+        <v>0.6345409611202319</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9627220201704905</v>
+        <v>0.7185628984138573</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2592991176928723</v>
+        <v>-0.08402193729362539</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.551323581354529</v>
+        <v>0.7009951818118163</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6065526363140731</v>
+        <v>0.6517983089787567</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.05522905495954411</v>
+        <v>0.04919687283305962</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7079758575992748</v>
+        <v>0.6341408862487742</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9846144783502357</v>
+        <v>0.7204046526370779</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2766386207509609</v>
+        <v>-0.08626376638830369</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7080457555056703</v>
+        <v>0.6994582584091362</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9813485063730141</v>
+        <v>0.65108101548879</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2733027508673438</v>
+        <v>0.04837724292034618</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6964712679194841</v>
+        <v>0.7007925503971146</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9471223424441118</v>
+        <v>0.6536403672562433</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2506510745246276</v>
+        <v>0.04715218314087133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4791245847132694</v>
+        <v>0.7016140540709986</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4732764813882495</v>
+        <v>0.6476298964539775</v>
       </c>
       <c r="D33" t="n">
-        <v>0.005848103325019838</v>
+        <v>0.05398415761702113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9786350684967103</v>
+        <v>0.5068017999841961</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7129209677057446</v>
+        <v>0.449029271194024</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2657141007909657</v>
+        <v>0.05777252879017208</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7063500850185951</v>
+        <v>0.4896296469852716</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9850018684986388</v>
+        <v>0.6421282258478271</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2786517834800437</v>
+        <v>-0.1524985788625556</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7075049589092895</v>
+        <v>0.7007525228927689</v>
       </c>
       <c r="C36" t="n">
-        <v>0.984466361181045</v>
+        <v>0.648756880077463</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2769614022717555</v>
+        <v>0.05199564281530589</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7087644488721103</v>
+        <v>0.4373589966746061</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9848400699767371</v>
+        <v>0.5499312283237971</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2760756211046268</v>
+        <v>-0.1125722316491911</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7070299578720003</v>
+        <v>0.6991691465457109</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9843369831492002</v>
+        <v>0.649459248609804</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2773070252771999</v>
+        <v>0.04970989793590697</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7100133654897186</v>
+        <v>0.6275148968031022</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9842124985572724</v>
+        <v>0.7144548788373608</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2741991330675538</v>
+        <v>-0.08693998203425857</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7092691750800795</v>
+        <v>0.6205419740285953</v>
       </c>
       <c r="C40" t="n">
-        <v>0.984343030075155</v>
+        <v>0.7121059392108033</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2750738549950755</v>
+        <v>-0.091563965182208</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9858114886016214</v>
+        <v>0.6288329345170257</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7179341252293979</v>
+        <v>0.7169021215506752</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2678773633722235</v>
+        <v>-0.08806918703364952</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.70617938863604</v>
+        <v>0.4115152780740801</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9854460978803321</v>
+        <v>0.6809647981224735</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2792667092442921</v>
+        <v>-0.2694495200483933</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9826165973691494</v>
+        <v>0.6278478809408818</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7150045053124078</v>
+        <v>0.714121234917971</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2676120920567416</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.7093731243883705</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.9840587767064968</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-0.2746856523181262</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.9830592326328765</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.7166645927661424</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.2663946398667342</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.9809437641670797</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.7152345925991574</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.2657091715679223</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.9834472340949445</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.7162685471273752</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.2671786869675693</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.9708643867910056</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.7114214029096002</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.2594429838814054</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0.6993554430281002</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.9334640479250405</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-0.2341086048969403</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0.7065302208558698</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.9830575348067662</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-0.2765273139508964</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0.205995619086806</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.7390424211330922</v>
-      </c>
-      <c r="D51" t="n">
-        <v>-0.5330468020462862</v>
+        <v>-0.08627335397708913</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,669 +457,941 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.377137726415987</v>
+        <v>0.767040775846468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6819230203249801</v>
+        <v>0.5633337927312394</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3047852939089931</v>
+        <v>0.2037069831152286</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5067129829003074</v>
+        <v>0.7890969352172152</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6236056588043462</v>
+        <v>0.6080653091594068</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1168926759040387</v>
+        <v>0.1810316260578084</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4826879696520813</v>
+        <v>0.1074831177064147</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6381519303469889</v>
+        <v>0.4380267793737014</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1554639606949076</v>
+        <v>-0.3305436616672867</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5821360344750989</v>
+        <v>0.8028929296470924</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3890671215833203</v>
+        <v>0.5942566951528361</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1930689128917786</v>
+        <v>0.2086362344942563</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5939028475711893</v>
+        <v>0.6091501617065114</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3708415712880428</v>
+        <v>0.160180296181271</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2230612762831464</v>
+        <v>0.4489698655252404</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4526094186033047</v>
+        <v>0.8058930834929726</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6554864030257319</v>
+        <v>0.6134527267895611</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2028769844224272</v>
+        <v>0.1924403567034115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007144722440186396</v>
+        <v>0.6096619679307549</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00200729846300878</v>
+        <v>0.1753383927057326</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005137423977177617</v>
+        <v>0.4343235752250223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4210779910000516</v>
+        <v>0.03421404898621972</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5318215606254093</v>
+        <v>0.09536431840547745</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1107435696253578</v>
+        <v>-0.06115026941925773</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6217739390885568</v>
+        <v>0.227285628422287</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7178644499294237</v>
+        <v>0.3389551875186155</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09609051084086684</v>
+        <v>-0.1116695590963285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4999689484462459</v>
+        <v>0.7437757809370364</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6304834817185002</v>
+        <v>0.7328072899273839</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1305145332722543</v>
+        <v>0.01096849100965258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3748139492863968</v>
+        <v>0.8088533338169127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6591115689430123</v>
+        <v>0.5980925157762055</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2842976196566154</v>
+        <v>0.2107608180407072</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5054689840253346</v>
+        <v>0.1030640347107548</v>
       </c>
       <c r="C13" t="n">
-        <v>0.517645920346168</v>
+        <v>0.7382891468778049</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.01217693632083339</v>
+        <v>-0.6352251121670501</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6350377587486356</v>
+        <v>0.03424150535575095</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5722440249060337</v>
+        <v>0.6692315745455772</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0627937338426019</v>
+        <v>-0.6349900691898263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4866146808238492</v>
+        <v>0.7900636078172943</v>
       </c>
       <c r="C15" t="n">
-        <v>0.628376371919688</v>
+        <v>0.6409342034924033</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1417616910958387</v>
+        <v>0.1491294043248911</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7018791914916932</v>
+        <v>0.6994042096082311</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6514921141876674</v>
+        <v>0.7371285598586745</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05038707730402581</v>
+        <v>-0.03772435025044341</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5121194266111841</v>
+        <v>0.6043465610260021</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4672752066773882</v>
+        <v>0.1628486308759177</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04484421993379595</v>
+        <v>0.4414979301500844</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5114603801548535</v>
+        <v>0.8000645573101466</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4950245861112515</v>
+        <v>0.6466499182709565</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01643579404360201</v>
+        <v>0.1534146390391901</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5117438699026333</v>
+        <v>0.6056234586166426</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5783520655087575</v>
+        <v>0.1604405793365029</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.06660819560612419</v>
+        <v>0.4451828792801397</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3944422820523952</v>
+        <v>0.8038434440790084</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6323206089811551</v>
+        <v>0.6260047906232725</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2378783269287599</v>
+        <v>0.1778386534557359</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6241900753099733</v>
+        <v>0.7162783419274782</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7123033824506657</v>
+        <v>0.7359484765810989</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08811330714069243</v>
+        <v>-0.01967013465362066</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3953240055330086</v>
+        <v>0.2439248941282591</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6374874687148173</v>
+        <v>0.3789639734631957</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2421634631818088</v>
+        <v>-0.1350390793349366</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3696126804517221</v>
+        <v>0.8017342844640312</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6587925800627129</v>
+        <v>0.5852454325290969</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2891798996109908</v>
+        <v>0.2164888519349343</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5298472494069106</v>
+        <v>0.8038037012084979</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5849256027020964</v>
+        <v>0.5897537300787532</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.05507835329518573</v>
+        <v>0.2140499711297447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6271924553240629</v>
+        <v>0.7799837060431923</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7143641137674952</v>
+        <v>0.5701617749127452</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08717165844343233</v>
+        <v>0.2098219311304471</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6269192653790212</v>
+        <v>0.8101404206024271</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7130312295005876</v>
+        <v>0.6031186103839665</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.08611196412156641</v>
+        <v>0.2070218102184606</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6976248884636664</v>
+        <v>0.786734576144667</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6485031086644256</v>
+        <v>0.5758567593321794</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04912177979924082</v>
+        <v>0.2108778168124876</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6345409611202319</v>
+        <v>0.245706803390794</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7185628984138573</v>
+        <v>0.2510328063763751</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08402193729362539</v>
+        <v>-0.005326002985581058</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7009951818118163</v>
+        <v>0.806235561202797</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6517983089787567</v>
+        <v>0.5926265479819841</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04919687283305962</v>
+        <v>0.2136090132208129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6341408862487742</v>
+        <v>0.8038054617182966</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7204046526370779</v>
+        <v>0.589423504224574</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.08626376638830369</v>
+        <v>0.2143819574937226</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6994582584091362</v>
+        <v>0.8058313639144946</v>
       </c>
       <c r="C31" t="n">
-        <v>0.65108101548879</v>
+        <v>0.594597866534432</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04837724292034618</v>
+        <v>0.2112334973800626</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7007925503971146</v>
+        <v>0.7996389845184582</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6536403672562433</v>
+        <v>0.6477545807030128</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04715218314087133</v>
+        <v>0.1518844038154453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7016140540709986</v>
+        <v>0.7678551249262017</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6476298964539775</v>
+        <v>0.6889662778625419</v>
       </c>
       <c r="D33" t="n">
-        <v>0.05398415761702113</v>
+        <v>0.07888884706365973</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5068017999841961</v>
+        <v>0.8069740231505353</v>
       </c>
       <c r="C34" t="n">
-        <v>0.449029271194024</v>
+        <v>0.6141861184097147</v>
       </c>
       <c r="D34" t="n">
-        <v>0.05777252879017208</v>
+        <v>0.1927879047408206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4896296469852716</v>
+        <v>0.687912651683256</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6421282258478271</v>
+        <v>0.7330557203417206</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1524985788625556</v>
+        <v>-0.04514306865846462</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7007525228927689</v>
+        <v>0.6847477157423233</v>
       </c>
       <c r="C36" t="n">
-        <v>0.648756880077463</v>
+        <v>0.7332718914357892</v>
       </c>
       <c r="D36" t="n">
-        <v>0.05199564281530589</v>
+        <v>-0.0485241756934659</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4373589966746061</v>
+        <v>0.8061549946056683</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5499312283237971</v>
+        <v>0.5990716422912816</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1125722316491911</v>
+        <v>0.2070833523143867</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6991691465457109</v>
+        <v>0.8091612716094314</v>
       </c>
       <c r="C38" t="n">
-        <v>0.649459248609804</v>
+        <v>0.6005206470931195</v>
       </c>
       <c r="D38" t="n">
-        <v>0.04970989793590697</v>
+        <v>0.2086406245163119</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6275148968031022</v>
+        <v>0.7021741170670932</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7144548788373608</v>
+        <v>0.739787175418996</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.08693998203425857</v>
+        <v>-0.03761305835190276</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6205419740285953</v>
+        <v>0.7902118591919947</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7121059392108033</v>
+        <v>0.6228607756436138</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.091563965182208</v>
+        <v>0.1673510835483809</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6288329345170257</v>
+        <v>0.6996571994630115</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7169021215506752</v>
+        <v>0.7372626583811959</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.08806918703364952</v>
+        <v>-0.03760545891818434</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4115152780740801</v>
+        <v>0.7032330314522266</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6809647981224735</v>
+        <v>0.7021441943730711</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2694495200483933</v>
+        <v>0.001088837079155525</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.7073903928108123</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7367915574134987</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.02940116460268638</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.6981439076561738</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6969858907213096</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.001158016934864281</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.7003086746386129</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.7059549296221761</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.005646254983563193</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.8088574277651446</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.5996742075735809</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.2091832201915637</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.7177397092502334</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.7398235138075625</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.02208380455732906</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.7735564631939952</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6796588399201882</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.09389762327380702</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.8082837179902207</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.5999008752307577</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.2083828427594629</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.7489318099354804</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7246993058503979</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.02423250408508248</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.5680024911265064</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.802173380475687</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.2341708893491806</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.7040492276644419</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7418297718079497</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.03778054414350784</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.7328200198270211</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7344583457933183</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.001638325966297205</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.8100192692281755</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.603700902227627</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.2063183670005485</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.1185156609663531</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6715779295777704</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.5530622686114173</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.8061980227491706</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.5932923834933929</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2129056392557778</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.7183148118110382</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7443288496400762</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.02601403782903799</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.8105186318678969</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6015250303415358</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.208993601526361</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>0.6278478809408818</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.714121234917971</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.08627335397708913</v>
+      <c r="B59" t="n">
+        <v>0.8071456430789734</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.5969803814841883</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.2101652615947851</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.1232152486730134</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6681961300652586</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.5449808813922452</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.767040775846468</v>
+        <v>0.7792240825291373</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5633337927312394</v>
+        <v>0.5930881698755295</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2037069831152286</v>
+        <v>0.1861359126536078</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7890969352172152</v>
+        <v>0.7749333945107759</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6080653091594068</v>
+        <v>0.638027735962725</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1810316260578084</v>
+        <v>0.1369056585480509</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1074831177064147</v>
+        <v>0.5234508468701781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4380267793737014</v>
+        <v>0.3943623508296566</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3305436616672867</v>
+        <v>0.1290884960405215</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8028929296470924</v>
+        <v>0.8060482737983224</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5942566951528361</v>
+        <v>0.6149920871116979</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2086362344942563</v>
+        <v>0.1910561866866245</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6091501617065114</v>
+        <v>0.7686822728018006</v>
       </c>
       <c r="C6" t="n">
-        <v>0.160180296181271</v>
+        <v>0.15015102014613</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4489698655252404</v>
+        <v>0.6185312526556705</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8058930834929726</v>
+        <v>0.6127704729199199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6134527267895611</v>
+        <v>0.8042605809765111</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1924403567034115</v>
+        <v>-0.1914901080565912</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6096619679307549</v>
+        <v>0.7574168721688489</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1753383927057326</v>
+        <v>0.1715910279476491</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4343235752250223</v>
+        <v>0.5858258442211998</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03421404898621972</v>
+        <v>0.0106320669249065</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09536431840547745</v>
+        <v>0.1059346050208952</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06115026941925773</v>
+        <v>-0.09530253809598871</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.227285628422287</v>
+        <v>0.4218612988154798</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3389551875186155</v>
+        <v>0.2996947283293856</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1116695590963285</v>
+        <v>0.1221665704860942</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7437757809370364</v>
+        <v>0.7413847559251333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7328072899273839</v>
+        <v>0.7125790517902398</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01096849100965258</v>
+        <v>0.02880570413489347</v>
       </c>
     </row>
     <row r="12">
@@ -617,781 +617,669 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8088533338169127</v>
+        <v>0.8081569117027311</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5980925157762055</v>
+        <v>0.615934213137698</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2107608180407072</v>
+        <v>0.192222698565033</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1030640347107548</v>
+        <v>0.06586540661404197</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7382891468778049</v>
+        <v>0.8049384776614648</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6352251121670501</v>
+        <v>-0.7390730710474228</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03424150535575095</v>
+        <v>0.7716559252283457</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6692315745455772</v>
+        <v>0.6387428708097876</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6349900691898263</v>
+        <v>0.1329130544185581</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7900636078172943</v>
+        <v>0.7343294848561325</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6409342034924033</v>
+        <v>0.7145516458336817</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1491294043248911</v>
+        <v>0.01977783902245078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6994042096082311</v>
+        <v>0.7579787384555577</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7371285598586745</v>
+        <v>0.1673236573803485</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.03772435025044341</v>
+        <v>0.5906550810752093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6043465610260021</v>
+        <v>0.7794452239999181</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1628486308759177</v>
+        <v>0.6866068603817062</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4414979301500844</v>
+        <v>0.09283836361821196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8000645573101466</v>
+        <v>0.7562884400067486</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6466499182709565</v>
+        <v>0.1623900015040446</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1534146390391901</v>
+        <v>0.593898438502704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6056234586166426</v>
+        <v>0.7963084543105178</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1604405793365029</v>
+        <v>0.6586302230925632</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4451828792801397</v>
+        <v>0.1376782312179545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8038434440790084</v>
+        <v>0.7362386425116565</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6260047906232725</v>
+        <v>0.7084100176865954</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1778386534557359</v>
+        <v>0.0278286248250611</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7162783419274782</v>
+        <v>0.3626749353074706</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7359484765810989</v>
+        <v>0.5592636127731684</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01967013465362066</v>
+        <v>-0.1965886774656978</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2439248941282591</v>
+        <v>0.8098785694421804</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3789639734631957</v>
+        <v>0.6213871528036231</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1350390793349366</v>
+        <v>0.1884914166385573</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8017342844640312</v>
+        <v>0.8083626134054754</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5852454325290969</v>
+        <v>0.619560621004526</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2164888519349343</v>
+        <v>0.1888019924009494</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8038037012084979</v>
+        <v>0.7984442917527472</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5897537300787532</v>
+        <v>0.5973360691743254</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2140499711297447</v>
+        <v>0.2011082225784219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7799837060431923</v>
+        <v>0.8064318346215538</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5701617749127452</v>
+        <v>0.6144292470417367</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2098219311304471</v>
+        <v>0.192002587579817</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8101404206024271</v>
+        <v>0.79960881790935</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6031186103839665</v>
+        <v>0.5999090522595014</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2070218102184606</v>
+        <v>0.1996997656498486</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.786734576144667</v>
+        <v>0.4167509683417889</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5758567593321794</v>
+        <v>0.2887355586227326</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2108778168124876</v>
+        <v>0.1280154097190563</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.245706803390794</v>
+        <v>0.8024223907896912</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2510328063763751</v>
+        <v>0.6039405800111409</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.005326002985581058</v>
+        <v>0.1984818107785503</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.806235561202797</v>
+        <v>0.8044701475007052</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5926265479819841</v>
+        <v>0.6100818735989112</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2136090132208129</v>
+        <v>0.194388273901794</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8038054617182966</v>
+        <v>0.8074314335124504</v>
       </c>
       <c r="C30" t="n">
-        <v>0.589423504224574</v>
+        <v>0.6171442093623757</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2143819574937226</v>
+        <v>0.1902872241500747</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8058313639144946</v>
+        <v>0.7864250853296202</v>
       </c>
       <c r="C31" t="n">
-        <v>0.594597866534432</v>
+        <v>0.647168145225438</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2112334973800626</v>
+        <v>0.1392569401041822</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7996389845184582</v>
+        <v>0.0783486608014998</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6477545807030128</v>
+        <v>0.771330141672804</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1518844038154453</v>
+        <v>-0.6929814808713042</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7678551249262017</v>
+        <v>0.6809677997422935</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6889662778625419</v>
+        <v>0.7108930344645774</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07888884706365973</v>
+        <v>-0.02992523472228392</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8069740231505353</v>
+        <v>0.809727854540926</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6141861184097147</v>
+        <v>0.6210911946996427</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1927879047408206</v>
+        <v>0.1886366598412833</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.687912651683256</v>
+        <v>0.8054942960904098</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7330557203417206</v>
+        <v>0.6152417108526657</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.04514306865846462</v>
+        <v>0.1902525852377441</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6847477157423233</v>
+        <v>0.695952101804065</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7332718914357892</v>
+        <v>0.7352442740637419</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0485241756934659</v>
+        <v>-0.03929217225967696</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8061549946056683</v>
+        <v>0.782511002477921</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5990716422912816</v>
+        <v>0.6336514019676676</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2070833523143867</v>
+        <v>0.1488596005102535</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8091612716094314</v>
+        <v>0.6943851326052827</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6005206470931195</v>
+        <v>0.7202311263493849</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2086406245163119</v>
+        <v>-0.02584599374410224</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7021741170670932</v>
+        <v>0.6944903932056743</v>
       </c>
       <c r="C39" t="n">
-        <v>0.739787175418996</v>
+        <v>0.7274231249397988</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.03761305835190276</v>
+        <v>-0.03293273173412448</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7902118591919947</v>
+        <v>0.7377252121680437</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6228607756436138</v>
+        <v>0.7121375885958141</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1673510835483809</v>
+        <v>0.02558762357222955</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6996571994630115</v>
+        <v>0.8065051298777188</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7372626583811959</v>
+        <v>0.6164520332810767</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.03760545891818434</v>
+        <v>0.1900530965966422</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7032330314522266</v>
+        <v>0.7308112082098961</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7021441943730711</v>
+        <v>0.7178334345145658</v>
       </c>
       <c r="D42" t="n">
-        <v>0.001088837079155525</v>
+        <v>0.01297777369533026</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7073903928108123</v>
+        <v>0.7325033848795953</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7367915574134987</v>
+        <v>0.7209802000030355</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.02940116460268638</v>
+        <v>0.01152318487655979</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6981439076561738</v>
+        <v>0.5855657563978859</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6969858907213096</v>
+        <v>0.8124708602932973</v>
       </c>
       <c r="D44" t="n">
-        <v>0.001158016934864281</v>
+        <v>-0.2269051038954114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7003086746386129</v>
+        <v>0.6790816735848414</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7059549296221761</v>
+        <v>0.7533792264313259</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.005646254983563193</v>
+        <v>-0.07429755284648454</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8088574277651446</v>
+        <v>0.6484944552536152</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5996742075735809</v>
+        <v>0.7967150580488979</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2091832201915637</v>
+        <v>-0.1482206027952827</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7177397092502334</v>
+        <v>0.6973889637305556</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7398235138075625</v>
+        <v>0.7268213745894232</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.02208380455732906</v>
+        <v>-0.02943241085886761</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7735564631939952</v>
+        <v>0.7226523957063795</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6796588399201882</v>
+        <v>0.7169189101549588</v>
       </c>
       <c r="D48" t="n">
-        <v>0.09389762327380702</v>
+        <v>0.005733485551420725</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8082837179902207</v>
+        <v>0.8090114920714433</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5999008752307577</v>
+        <v>0.6195116075192542</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2083828427594629</v>
+        <v>0.1894998845521891</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7489318099354804</v>
+        <v>0.1356522625568395</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7246993058503979</v>
+        <v>0.8076469364711475</v>
       </c>
       <c r="D50" t="n">
-        <v>0.02423250408508248</v>
+        <v>-0.671994673914308</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5680024911265064</v>
+        <v>0.8078065161238128</v>
       </c>
       <c r="C51" t="n">
-        <v>0.802173380475687</v>
+        <v>0.6182216885178426</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2341708893491806</v>
+        <v>0.1895848276059702</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7040492276644419</v>
+        <v>0.733888110269437</v>
       </c>
       <c r="C52" t="n">
-        <v>0.7418297718079497</v>
+        <v>0.7157554748041463</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.03778054414350784</v>
+        <v>0.01813263546529076</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7328200198270211</v>
+        <v>0.1569558465199331</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7344583457933183</v>
+        <v>0.8044144120983079</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.001638325966297205</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.8100192692281755</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.603700902227627</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.2063183670005485</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0.1185156609663531</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.6715779295777704</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.5530622686114173</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.8061980227491706</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.5932923834933929</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.2129056392557778</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.7183148118110382</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.7443288496400762</v>
-      </c>
-      <c r="D57" t="n">
-        <v>-0.02601403782903799</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.8105186318678969</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.6015250303415358</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.208993601526361</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.8071456430789734</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.5969803814841883</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.2101652615947851</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.1232152486730134</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.6681961300652586</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.5449808813922452</v>
+        <v>-0.6474585655783748</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_coassignment_summaries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7792240825291373</v>
+        <v>0.767040775846468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5930881698755295</v>
+        <v>0.5633337927312394</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1861359126536078</v>
+        <v>0.2037069831152286</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7749333945107759</v>
+        <v>0.7890969352172152</v>
       </c>
       <c r="C3" t="n">
-        <v>0.638027735962725</v>
+        <v>0.6080653091594068</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1369056585480509</v>
+        <v>0.1810316260578084</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5234508468701781</v>
+        <v>0.1074831177064147</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3943623508296566</v>
+        <v>0.4380267793737014</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1290884960405215</v>
+        <v>-0.3305436616672867</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8060482737983224</v>
+        <v>0.8028929296470924</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6149920871116979</v>
+        <v>0.5942566951528361</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1910561866866245</v>
+        <v>0.2086362344942563</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7686822728018006</v>
+        <v>0.6091501617065114</v>
       </c>
       <c r="C6" t="n">
-        <v>0.15015102014613</v>
+        <v>0.160180296181271</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6185312526556705</v>
+        <v>0.4489698655252404</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6127704729199199</v>
+        <v>0.8058930834929726</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8042605809765111</v>
+        <v>0.6134527267895611</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1914901080565912</v>
+        <v>0.1924403567034115</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7574168721688489</v>
+        <v>0.6096619679307549</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1715910279476491</v>
+        <v>0.1753383927057326</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5858258442211998</v>
+        <v>0.4343235752250223</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0106320669249065</v>
+        <v>0.03421404898621972</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1059346050208952</v>
+        <v>0.09536431840547745</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09530253809598871</v>
+        <v>-0.06115026941925773</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4218612988154798</v>
+        <v>0.227285628422287</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2996947283293856</v>
+        <v>0.3389551875186155</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1221665704860942</v>
+        <v>-0.1116695590963285</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7413847559251333</v>
+        <v>0.7437757809370364</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7125790517902398</v>
+        <v>0.7328072899273839</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02880570413489347</v>
+        <v>0.01096849100965258</v>
       </c>
     </row>
     <row r="12">
@@ -617,669 +617,781 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8081569117027311</v>
+        <v>0.8088533338169127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.615934213137698</v>
+        <v>0.5980925157762055</v>
       </c>
       <c r="D12" t="n">
-        <v>0.192222698565033</v>
+        <v>0.2107608180407072</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06586540661404197</v>
+        <v>0.1030640347107548</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8049384776614648</v>
+        <v>0.7382891468778049</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7390730710474228</v>
+        <v>-0.6352251121670501</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7716559252283457</v>
+        <v>0.03424150535575095</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6387428708097876</v>
+        <v>0.6692315745455772</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1329130544185581</v>
+        <v>-0.6349900691898263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7343294848561325</v>
+        <v>0.7900636078172943</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7145516458336817</v>
+        <v>0.6409342034924033</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01977783902245078</v>
+        <v>0.1491294043248911</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7579787384555577</v>
+        <v>0.6994042096082311</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1673236573803485</v>
+        <v>0.7371285598586745</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5906550810752093</v>
+        <v>-0.03772435025044341</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7794452239999181</v>
+        <v>0.6043465610260021</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6866068603817062</v>
+        <v>0.1628486308759177</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09283836361821196</v>
+        <v>0.4414979301500844</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7562884400067486</v>
+        <v>0.8000645573101466</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1623900015040446</v>
+        <v>0.6466499182709565</v>
       </c>
       <c r="D18" t="n">
-        <v>0.593898438502704</v>
+        <v>0.1534146390391901</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7963084543105178</v>
+        <v>0.6056234586166426</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6586302230925632</v>
+        <v>0.1604405793365029</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1376782312179545</v>
+        <v>0.4451828792801397</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7362386425116565</v>
+        <v>0.8038434440790084</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7084100176865954</v>
+        <v>0.6260047906232725</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0278286248250611</v>
+        <v>0.1778386534557359</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3626749353074706</v>
+        <v>0.7162783419274782</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5592636127731684</v>
+        <v>0.7359484765810989</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1965886774656978</v>
+        <v>-0.01967013465362066</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8098785694421804</v>
+        <v>0.2439248941282591</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6213871528036231</v>
+        <v>0.3789639734631957</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1884914166385573</v>
+        <v>-0.1350390793349366</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8083626134054754</v>
+        <v>0.8017342844640312</v>
       </c>
       <c r="C23" t="n">
-        <v>0.619560621004526</v>
+        <v>0.5852454325290969</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1888019924009494</v>
+        <v>0.2164888519349343</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7984442917527472</v>
+        <v>0.8038037012084979</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5973360691743254</v>
+        <v>0.5897537300787532</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2011082225784219</v>
+        <v>0.2140499711297447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8064318346215538</v>
+        <v>0.7799837060431923</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6144292470417367</v>
+        <v>0.5701617749127452</v>
       </c>
       <c r="D25" t="n">
-        <v>0.192002587579817</v>
+        <v>0.2098219311304471</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.79960881790935</v>
+        <v>0.8101404206024271</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5999090522595014</v>
+        <v>0.6031186103839665</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1996997656498486</v>
+        <v>0.2070218102184606</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4167509683417889</v>
+        <v>0.786734576144667</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2887355586227326</v>
+        <v>0.5758567593321794</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1280154097190563</v>
+        <v>0.2108778168124876</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8024223907896912</v>
+        <v>0.245706803390794</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6039405800111409</v>
+        <v>0.2510328063763751</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1984818107785503</v>
+        <v>-0.005326002985581058</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8044701475007052</v>
+        <v>0.806235561202797</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6100818735989112</v>
+        <v>0.5926265479819841</v>
       </c>
       <c r="D29" t="n">
-        <v>0.194388273901794</v>
+        <v>0.2136090132208129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8074314335124504</v>
+        <v>0.8038054617182966</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6171442093623757</v>
+        <v>0.589423504224574</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1902872241500747</v>
+        <v>0.2143819574937226</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7864250853296202</v>
+        <v>0.8058313639144946</v>
       </c>
       <c r="C31" t="n">
-        <v>0.647168145225438</v>
+        <v>0.594597866534432</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1392569401041822</v>
+        <v>0.2112334973800626</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0783486608014998</v>
+        <v>0.7996389845184582</v>
       </c>
       <c r="C32" t="n">
-        <v>0.771330141672804</v>
+        <v>0.6477545807030128</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6929814808713042</v>
+        <v>0.1518844038154453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6809677997422935</v>
+        <v>0.7678551249262017</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7108930344645774</v>
+        <v>0.6889662778625419</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.02992523472228392</v>
+        <v>0.07888884706365973</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.809727854540926</v>
+        <v>0.8069740231505353</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6210911946996427</v>
+        <v>0.6141861184097147</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1886366598412833</v>
+        <v>0.1927879047408206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8054942960904098</v>
+        <v>0.687912651683256</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6152417108526657</v>
+        <v>0.7330557203417206</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1902525852377441</v>
+        <v>-0.04514306865846462</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.695952101804065</v>
+        <v>0.6847477157423233</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7352442740637419</v>
+        <v>0.7332718914357892</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.03929217225967696</v>
+        <v>-0.0485241756934659</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.782511002477921</v>
+        <v>0.8061549946056683</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6336514019676676</v>
+        <v>0.5990716422912816</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1488596005102535</v>
+        <v>0.2070833523143867</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6943851326052827</v>
+        <v>0.8091612716094314</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7202311263493849</v>
+        <v>0.6005206470931195</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.02584599374410224</v>
+        <v>0.2086406245163119</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6944903932056743</v>
+        <v>0.7021741170670932</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7274231249397988</v>
+        <v>0.739787175418996</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.03293273173412448</v>
+        <v>-0.03761305835190276</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7377252121680437</v>
+        <v>0.7902118591919947</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7121375885958141</v>
+        <v>0.6228607756436138</v>
       </c>
       <c r="D40" t="n">
-        <v>0.02558762357222955</v>
+        <v>0.1673510835483809</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8065051298777188</v>
+        <v>0.6996571994630115</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6164520332810767</v>
+        <v>0.7372626583811959</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1900530965966422</v>
+        <v>-0.03760545891818434</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7308112082098961</v>
+        <v>0.7032330314522266</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7178334345145658</v>
+        <v>0.7021441943730711</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01297777369533026</v>
+        <v>0.001088837079155525</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7325033848795953</v>
+        <v>0.7073903928108123</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7209802000030355</v>
+        <v>0.7367915574134987</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01152318487655979</v>
+        <v>-0.02940116460268638</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5855657563978859</v>
+        <v>0.6981439076561738</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8124708602932973</v>
+        <v>0.6969858907213096</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2269051038954114</v>
+        <v>0.001158016934864281</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6790816735848414</v>
+        <v>0.7003086746386129</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7533792264313259</v>
+        <v>0.7059549296221761</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.07429755284648454</v>
+        <v>-0.005646254983563193</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6484944552536152</v>
+        <v>0.8088574277651446</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7967150580488979</v>
+        <v>0.5996742075735809</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1482206027952827</v>
+        <v>0.2091832201915637</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6973889637305556</v>
+        <v>0.7177397092502334</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7268213745894232</v>
+        <v>0.7398235138075625</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.02943241085886761</v>
+        <v>-0.02208380455732906</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7226523957063795</v>
+        <v>0.7735564631939952</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7169189101549588</v>
+        <v>0.6796588399201882</v>
       </c>
       <c r="D48" t="n">
-        <v>0.005733485551420725</v>
+        <v>0.09389762327380702</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8090114920714433</v>
+        <v>0.8082837179902207</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6195116075192542</v>
+        <v>0.5999008752307577</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1894998845521891</v>
+        <v>0.2083828427594629</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1356522625568395</v>
+        <v>0.7489318099354804</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8076469364711475</v>
+        <v>0.7246993058503979</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.671994673914308</v>
+        <v>0.02423250408508248</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8078065161238128</v>
+        <v>0.5680024911265064</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6182216885178426</v>
+        <v>0.802173380475687</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1895848276059702</v>
+        <v>-0.2341708893491806</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.733888110269437</v>
+        <v>0.7040492276644419</v>
       </c>
       <c r="C52" t="n">
-        <v>0.7157554748041463</v>
+        <v>0.7418297718079497</v>
       </c>
       <c r="D52" t="n">
-        <v>0.01813263546529076</v>
+        <v>-0.03778054414350784</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.7328200198270211</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7344583457933183</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.001638325966297205</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.8100192692281755</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.603700902227627</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.2063183670005485</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.1185156609663531</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6715779295777704</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.5530622686114173</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.8061980227491706</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.5932923834933929</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2129056392557778</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.7183148118110382</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7443288496400762</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.02601403782903799</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.8105186318678969</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6015250303415358</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.208993601526361</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.8071456430789734</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.5969803814841883</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.2101652615947851</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0.1569558465199331</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.8044144120983079</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-0.6474585655783748</v>
+      <c r="B60" t="n">
+        <v>0.1232152486730134</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6681961300652586</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.5449808813922452</v>
       </c>
     </row>
   </sheetData>
